--- a/data/descargas/cargos_recurrentes_2026-02.xlsx
+++ b/data/descargas/cargos_recurrentes_2026-02.xlsx
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-03-2026 07:22 a. m. </t>
+          <t xml:space="preserve">Reporte generado: 01-03-2026 07:49 a. m. </t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
